--- a/cleaning_pipeline_R/neotree_scripts/mwi-scripts/Kasungu District Hospital Neotree Discharge - metadata.xlsx
+++ b/cleaning_pipeline_R/neotree_scripts/mwi-scripts/Kasungu District Hospital Neotree Discharge - metadata.xlsx
@@ -1393,7 +1393,7 @@
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
       </c>
       <c r="N15" t="str">
-        <v>[{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ASP","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Birth Asphyxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BR","valueLabel":"Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CAI","valueLabel":"Congenital abnormality incompatible with life","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FO","valueLabel":"Fluid Overload","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPG","valueLabel":"Hypoglycaermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPT","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypoxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MEN","valueLabel":"Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PRRDS","valueLabel":"Prematurity with RDS","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDNT","valueLabel":"Respiratory distress of newborn (Term)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RF","valueLabel":"Respiratory Failure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SH","valueLabel":"Shock","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"UNK","valueLabel":"Unknown","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ASP","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BA","valueLabel":"Birth Asphyxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BR","valueLabel":"Bronchiolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CAI","valueLabel":"Congenital abnormality incompatible with life","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"FO","valueLabel":"Fluid Overload","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPG","valueLabel":"Hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYPT","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypoxia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MEN","valueLabel":"Meningitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PRRDS","valueLabel":"Prematurity with RDS","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDNT","valueLabel":"Respiratory distress of newborn (Term)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RF","valueLabel":"Respiratory Failure","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"SH","valueLabel":"Shock","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O15" t="str">
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
@@ -1529,7 +1529,7 @@
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
       </c>
       <c r="N17" t="str">
-        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AS","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BDN","valueLabel":"Bleeding Disorder of the Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DEHY","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ELIM","valueLabel":"Electrolyte Imbalance","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"G","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYGL","valueLabel":"Hypoglycemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NS","valueLabel":"Neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Prematurity with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
+        <v>[{"value":"Norm","valueLabel":"NONE","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AN","valueLabel":"Anaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AP","valueLabel":"Apnea","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"AS","valueLabel":"Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BDN","valueLabel":"Bleeding Disorder of the Newborn","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"BO","valueLabel":"Bowel Obstruction","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"CHD","valueLabel":"Congenital Heart Disease","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"DEHY","valueLabel":"Dehydration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"ELIM","valueLabel":"Electrolyte Imbalance","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"G","valueLabel":"Gastroschisis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"GA","valueLabel":"Gastroenteritis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypoglycaemia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HYP","valueLabel":"Hypothermia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"HIE","valueLabel":"Hypoxic Ischaemic Encephalopathy (HIE)","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"LBW","valueLabel":"Low Birth Weight","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MA","valueLabel":"Meconium Aspiration","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"MAL","valueLabel":"Malnutrition","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NEC","valueLabel":"Necrotising Enterocolitis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NS","valueLabel":"Neonatal sepsis","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"NT","valueLabel":"Neonatal Tetenus","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PremRD","valueLabel":"Prematurity with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"TermRD","valueLabel":"Term baby with Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"RDS","valueLabel":"Respiratory Distress","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"PN","valueLabel":"Pneumonia","disabledOtherOptionsIfSelected":false,"forbidWIth":[]},{"value":"OTH","valueLabel":"Other","disabledOtherOptionsIfSelected":false,"forbidWIth":[]}]</v>
       </c>
       <c r="O17" t="str">
         <v>$NeoTreeOutcome = 'NND&lt;24' or $NeoTreeOutcome = 'NND&gt;24'</v>
@@ -1869,7 +1869,7 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>[{"value":"STB","valueLabel":"Stillbirth - born dead at &gt; 28 wks"},{"value":"PND","valueLabel":"Born alive at &gt; 28 wks but dead on arrival"},{"value":"AB","valueLabel":"Abortion - born dead at &lt; 28 wks"},{"value":"DU","valueLabel":"Dumped Baby"}]</v>
+        <v>[{"value":"STB","valueLabel":"Stillbirth - born dead at &gt; 28 wks"},{"value":"PND","valueLabel":"Born alive at &gt; 28 wks but dead on arrival to Ethel"},{"value":"AB","valueLabel":"Abortion - born dead at &lt; 28 wks"},{"value":"DU","valueLabel":"Dumped Baby"}]</v>
       </c>
       <c r="O22" t="str">
         <v>$NeoTreeOutcome = 'BID'</v>
@@ -2000,7 +2000,7 @@
         <v/>
       </c>
       <c r="K24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L24" t="str">
         <v>No</v>
@@ -2985,7 +2985,7 @@
         <v/>
       </c>
       <c r="N38" t="str">
-        <v>[{"value":"AB","valueLabel":"Abscess"},{"value":"An","valueLabel":"Anaemia"},{"value":"AL","valueLabel":"Albinism"},{"value":"Apn","valueLabel":"Apnoea of prematurity"},{"value":"BA","valueLabel":"Birth Asphyxia/HIE"},{"value":"BI","valueLabel":"Birth Injury"},{"value":"BDN","valueLabel":"Bleeding Disorder of a Newborn"},{"value":"BC","valueLabel":"Blood Clotting Disorder"},{"value":"BO","valueLabel":"Bowel Obstruction"},{"value":"BRON","valueLabel":"Bronchiolitis"},{"value":"CEP","valueLabel":"Cephalohematoma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CS","valueLabel":"Congenital Syphillis"},{"value":"CHD","valueLabel":"Congenital Heart Disease"},{"value":"DWT","valueLabel":"Down Sydrome/Trisomy 21"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"FTT","valueLabel":"Failure to Thrive"},{"value":"GAN","valueLabel":"Gangrene"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"HYP","valueLabel":"Hypoglycemia"},{"value":"HIVX","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LA","valueLabel":"Laryngomalacia"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"HBW","valueLabel":"High Birth Weight (&gt;4000g at birth)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MD","valueLabel":"Musculoskeletal Abnormalities"},{"value":"NEC","valueLabel":"Necrotising Enterocolitis"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Risk factors for sepsis (but sepsis ruled out)"},{"value":"NT","valueLabel":"Neonatal Tetenus"},{"value":"OT","valueLabel":"Oral Thrush"},{"value":"OPNE","valueLabel":"Opthalmia Neonatolum"},{"value":"NB","valueLabel":"Normal Baby"},{"value":"PR","valueLabel":"Prematurity"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory Distress"},{"value":"TermRD","valueLabel":"Term baby with Respiratory Distress"},{"value":"PS","valueLabel":"Prune Belly Syndrome"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"SKI","valueLabel":"Skin Infection"},{"value":"SEB","valueLabel":"Syphillis Exposed Baby"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"TR13","valueLabel":"Trisomy 13"},{"value":"OSC","valueLabel":"Other Surgical Conditions"},{"value":"OTH","valueLabel":"Other"}]</v>
+        <v>[{"value":"AB","valueLabel":"Abscess"},{"value":"An","valueLabel":"Anaemia"},{"value":"AL","valueLabel":"Albinism"},{"value":"Apn","valueLabel":"Apnoea of prematurity"},{"value":"BA","valueLabel":"Birth Asphyxia/HIE"},{"value":"BI","valueLabel":"Birth Injury"},{"value":"BDN","valueLabel":"Bleeding Disorder of a Newborn"},{"value":"BC","valueLabel":"Blood Clotting Disorder"},{"value":"BO","valueLabel":"Bowel Obstruction"},{"value":"BRON","valueLabel":"Bronchiolitis"},{"value":"CEP","valueLabel":"Cephalohematoma"},{"value":"Cong","valueLabel":"Congenital Abnormality"},{"value":"CS","valueLabel":"Congenital Syphillis"},{"value":"CHD","valueLabel":"Congenital Heart Disease"},{"value":"DWT","valueLabel":"Down Sydrome/Trisomy 21"},{"value":"Dhyd","valueLabel":"Dehydration"},{"value":"FTT","valueLabel":"Failure to Thrive"},{"value":"GAN","valueLabel":"Gangrene"},{"value":"GSchis","valueLabel":"Gastroschisis"},{"value":"HYP","valueLabel":"Hypoglycaemia"},{"value":"HIVX","valueLabel":"HIV Exposed"},{"value":"J","valueLabel":"Jaundice"},{"value":"LA","valueLabel":"Laryngomalacia"},{"value":"LBW","valueLabel":"Low Birth Weight"},{"value":"HBW","valueLabel":"High Birth Weight (&gt;4000g at birth)"},{"value":"MA","valueLabel":"Possible Meconium Aspiration"},{"value":"MD","valueLabel":"Musculoskeletal Abnormalities"},{"value":"NEC","valueLabel":"Necrotising Enterocolitis"},{"value":"EONS","valueLabel":"Neonatal Sepsis - Early Onset (EONS)"},{"value":"LONS","valueLabel":"Neonatal Sepsis - Late Onset (LONS)"},{"value":"NSepNC","valueLabel":"Risk factors for sepsis (but sepsis ruled out)"},{"value":"NT","valueLabel":"Neonatal Tetenus"},{"value":"OT","valueLabel":"Oral Thrush"},{"value":"OPNE","valueLabel":"Opthalmia Neonatolum"},{"value":"NB","valueLabel":"Normal Baby"},{"value":"PR","valueLabel":"Prematurity"},{"value":"PremRD","valueLabel":"Prematurity with Respiratory Distress"},{"value":"TermRD","valueLabel":"Term baby with Respiratory Distress"},{"value":"PS","valueLabel":"Prune Belly Syndrome"},{"value":"PN","valueLabel":"Pneumonia"},{"value":"SKI","valueLabel":"Skin Infection"},{"value":"SEB","valueLabel":"Syphillis Exposed Baby"},{"value":"TTN","valueLabel":"Transient Tachypnoea of Newborn (TTN)"},{"value":"TR13","valueLabel":"Trisomy 13"},{"value":"OSC","valueLabel":"Other Surgical Conditions"},{"value":"OTH","valueLabel":"Other"}]</v>
       </c>
       <c r="O38" t="str">
         <v>$NeoTreeOutcome = 'DC' or $NeoTreeOutcome = 'ABS' or $NeoTreeOutcome = 'TRH' or $NeoTreeOutcome = 'TRO' or $NeoTreeOutcome = 'DCR' or $NeoTreeOutcome  = 'DPC' or $NeoTreeOutcome = 'DCKMC'</v>
@@ -7068,10 +7068,10 @@
         <v/>
       </c>
       <c r="K98" t="str">
+        <v>No</v>
+      </c>
+      <c r="L98" t="str">
         <v>Yes</v>
-      </c>
-      <c r="L98" t="str">
-        <v>No</v>
       </c>
       <c r="M98" t="str">
         <v/>
@@ -7204,7 +7204,7 @@
         <v/>
       </c>
       <c r="K100" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L100" t="str">
         <v>No</v>
@@ -7272,7 +7272,7 @@
         <v/>
       </c>
       <c r="K101" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L101" t="str">
         <v>No</v>
@@ -7340,7 +7340,7 @@
         <v/>
       </c>
       <c r="K102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="L102" t="str">
         <v>No</v>
@@ -10409,7 +10409,7 @@
         <v/>
       </c>
       <c r="N147" t="str">
-        <v>[{"value":"CaBa","valueLabel":"Carien Banda"},{"value":"DaNy","valueLabel":"Davie Flemmings Nyirenda"},{"value":"DoCh","valueLabel":"Dorica Chisasula"},{"value":"EnTh","valueLabel":"Enala Theu"},{"value":"FaNt","valueLabel":"Faith Nthala"},{"value":"HaCh","valueLabel":"Hannock Chingondo"},{"value":"JoMw","valueLabel":"John Mwafulirwa"},{"value":"LiMu","valueLabel":"Dr Linily Musa"},{"value":"EnTh","valueLabel":"Enala Theu"},{"value":"FaNt","valueLabel":"Faith Nthala"},{"value":"MaFr","valueLabel":"Mark Frazer"},{"value":"MaMn","valueLabel":"Martha Mndzeka"},{"value":"NeMa","valueLabel":"Nellie Mandah"},{"value":"OlMk","valueLabel":"Olive Mkoma"},{"value":"PhNa","valueLabel":"Philomena Nambuzi"},{"value":"RuMa","valueLabel":"Ruth Mases"},{"value":"TiMw","valueLabel":"Tiwonge Mwale"},{"value":"ViGa","valueLabel":"Victoria Gausi"},{"value":"WeMp","valueLabel":"Wezzie Mphande"},{"value":"WiCh","valueLabel":"Winfred Chunda"},{"value":"OTH","valueLabel":"Other/ Student"}]</v>
+        <v>[{"value":"CaBa","valueLabel":"Carien Banda"},{"value":"DaNy","valueLabel":"Davie Flemmings Nyirenda"},{"value":"DoCh","valueLabel":"Dorica Chisasula"},{"value":"LiMu","valueLabel":"Dr Linily Musa"},{"value":"MaFr","valueLabel":"Mark Frazer"},{"value":"MaMn","valueLabel":"Martha Mndzeka"},{"value":"NeMa","valueLabel":"Nellie Mandah"},{"value":"OlMk","valueLabel":"Olive Mkoma"},{"value":"PhNa","valueLabel":"Philomena Nambuzi"},{"value":"TiMw","valueLabel":"Tiwonge Mwale"},{"value":"ViGa","valueLabel":"Victoria Gausi"},{"value":"WeMp","valueLabel":"Wezzie Mphande"},{"value":"WiCh","valueLabel":"Winfred Chunda"},{"value":"OliChib","valueLabel":"Olive Chibvumbi"},{"value":"BelJm","valueLabel":"Beleya James"},{"value":"OTH","valueLabel":"Other/ Student"},{"value":"JAWA","valueLabel":"Jacqueline Wallace"}]</v>
       </c>
       <c r="O147" t="str">
         <v/>
